--- a/learning/python/mini-projects/cmi/deposit_analysis.xlsx
+++ b/learning/python/mini-projects/cmi/deposit_analysis.xlsx
@@ -486,20 +486,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>金城项目英国OF_202505.pdf</t>
+          <t>OnSemi-DICT - Order Form (GTC) - 06162026 Updated.doc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>江苏⾦珹智能存储设备有限公司</t>
+          <t>Semiconductor Components Industries LLC</t>
         </is>
       </c>
       <c r="C2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Not Specified</t>
+          <t>Nil</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -507,24 +507,26 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Payment due 10 days; milestone payments: 10% before entry, 20% within two weeks, 60% at 80% completion, 10% after acceptance</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>30 days</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>14850</v>
+      </c>
       <c r="J2" t="n">
-        <v>2557600</v>
+        <v>0</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>CNY</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>CMI may require a security deposit in specified form; value can be varied within 7 days if payment issues or financial changes; deposit applied to unpaid charges; must be restored if applied; released after full payment within 30 days of termination; does not relieve payment obligation</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Deposit type specified as Nil; no security deposit required as per checkbox. Security requirement clauses in remarks detail conditions for deposit variation and application, but not applicable since deposit is Nil.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
